--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N86_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N86_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.48491525424077</v>
+        <v>10.15379872881413</v>
       </c>
       <c r="D2" t="n">
-        <v>37.35812156701152</v>
+        <v>6.070694754639372</v>
       </c>
       <c r="E2" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F2" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.71856611527941</v>
+        <v>8.079266993732904</v>
       </c>
       <c r="D3" t="n">
-        <v>9.366038722909762</v>
+        <v>1.521981292472836</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F3" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.75228062025624</v>
+        <v>7.59724560079164</v>
       </c>
       <c r="D4" t="n">
-        <v>30.84361752397254</v>
+        <v>5.012087847645538</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F4" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.520010277088797</v>
+        <v>1.54700167002693</v>
       </c>
       <c r="D5" t="n">
-        <v>9.288903008253738</v>
+        <v>1.509446738841232</v>
       </c>
       <c r="E5" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F5" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.2567900342927</v>
+        <v>4.916728380572565</v>
       </c>
       <c r="D6" t="n">
-        <v>28.50037760213474</v>
+        <v>4.631311360346895</v>
       </c>
       <c r="E6" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F6" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.49197295737073</v>
+        <v>4.142445605572744</v>
       </c>
       <c r="D7" t="n">
-        <v>24.75939776686375</v>
+        <v>4.02340213711536</v>
       </c>
       <c r="E7" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F7" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.97103266908142</v>
+        <v>5.845292808725731</v>
       </c>
       <c r="D8" t="n">
-        <v>12.12629512753201</v>
+        <v>1.970522958223951</v>
       </c>
       <c r="E8" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F8" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>3.190476190476176</v>
+        <v>0.5184523809523786</v>
       </c>
       <c r="D9" t="n">
-        <v>15.70320187021719</v>
+        <v>2.551770303910293</v>
       </c>
       <c r="E9" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F9" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.99487488925768</v>
+        <v>2.436667169504373</v>
       </c>
       <c r="D10" t="n">
-        <v>26.5382329838098</v>
+        <v>4.312462859869092</v>
       </c>
       <c r="E10" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F10" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.22654618194085</v>
+        <v>2.474313754565388</v>
       </c>
       <c r="D11" t="n">
-        <v>9.517166995702372</v>
+        <v>1.546539636801636</v>
       </c>
       <c r="E11" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F11" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.912797564115654</v>
+        <v>1.285829604168794</v>
       </c>
       <c r="D12" t="n">
-        <v>24.08935353069985</v>
+        <v>3.914519948738725</v>
       </c>
       <c r="E12" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F12" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.11669351949746</v>
+        <v>3.756462696918337</v>
       </c>
       <c r="D13" t="n">
-        <v>5.321844648077751</v>
+        <v>0.8647997553126345</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F13" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.8446872138209</v>
+        <v>7.449761672245896</v>
       </c>
       <c r="D14" t="n">
-        <v>28.66336654837317</v>
+        <v>4.65779706411064</v>
       </c>
       <c r="E14" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F14" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.05576415201854</v>
+        <v>1.796561674703013</v>
       </c>
       <c r="D15" t="n">
-        <v>27.09310370482569</v>
+        <v>4.402629352034174</v>
       </c>
       <c r="E15" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F15" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.07554454210368</v>
+        <v>5.212275988091848</v>
       </c>
       <c r="D16" t="n">
-        <v>10.84301017827262</v>
+        <v>1.7619891539693</v>
       </c>
       <c r="E16" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F16" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>11.20042254243133</v>
+        <v>1.820068663145091</v>
       </c>
       <c r="D17" t="n">
-        <v>10.95108297326649</v>
+        <v>1.779550983155804</v>
       </c>
       <c r="E17" t="n">
-        <v>17.0933248932054</v>
+        <v>2.777665295145877</v>
       </c>
       <c r="F17" t="n">
-        <v>9.65941186723617</v>
+        <v>1.569654428425878</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
